--- a/sample-data/US-01/sample-po-missing-fields.xlsx
+++ b/sample-data/US-01/sample-po-missing-fields.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/sample-data/US-01/sample-po-missing-fields.xlsx
+++ b/sample-data/US-01/sample-po-missing-fields.xlsx
@@ -488,7 +488,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PURCHASE ORDER — INCOMPLETE (Demo)</t>
+          <t>PURCHASE ORDER — INCOMPLETE</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>PO-2026-EXCEL-002</t>
+          <t>PO-2026-10011</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Delta Energy Services</t>
+          <t>Riverside Mechanical Contractors</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Delta Energy, Remote Site, Texas</t>
+          <t>Riverside Mechanical, Project Site, TX</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SKU-PMP-6601</t>
+          <t>SKU-SHS-6601</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Centrifugal Pump 6 inch</t>
+          <t>Digital Shower Controller</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
